--- a/Figures/Heatmaps/Amp-heatmap.xlsx
+++ b/Figures/Heatmaps/Amp-heatmap.xlsx
@@ -19,76 +19,76 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="109">
   <si>
-    <t>T1</t>
-  </si>
-  <si>
-    <t>T2</t>
-  </si>
-  <si>
-    <t>T3</t>
-  </si>
-  <si>
-    <t>T4</t>
-  </si>
-  <si>
-    <t>T5</t>
-  </si>
-  <si>
-    <t>T6</t>
-  </si>
-  <si>
-    <t>T7</t>
-  </si>
-  <si>
-    <t>T8</t>
-  </si>
-  <si>
-    <t>T9</t>
-  </si>
-  <si>
-    <t>T10</t>
-  </si>
-  <si>
-    <t>T11</t>
-  </si>
-  <si>
-    <t>T12</t>
-  </si>
-  <si>
-    <t>T13</t>
-  </si>
-  <si>
-    <t>T14</t>
-  </si>
-  <si>
-    <t>T15</t>
-  </si>
-  <si>
-    <t>T16</t>
-  </si>
-  <si>
-    <t>T17</t>
-  </si>
-  <si>
-    <t>T18</t>
-  </si>
-  <si>
-    <t>T19</t>
-  </si>
-  <si>
-    <t>T20</t>
-  </si>
-  <si>
-    <t>T21</t>
-  </si>
-  <si>
-    <t>T22</t>
-  </si>
-  <si>
-    <t>T23</t>
-  </si>
-  <si>
-    <t>T24</t>
+    <t>TI</t>
+  </si>
+  <si>
+    <t>TII</t>
+  </si>
+  <si>
+    <t>TIIIa</t>
+  </si>
+  <si>
+    <t>TIII</t>
+  </si>
+  <si>
+    <t>TIV</t>
+  </si>
+  <si>
+    <t>TV</t>
+  </si>
+  <si>
+    <t>TVI</t>
+  </si>
+  <si>
+    <t>TVIIa</t>
+  </si>
+  <si>
+    <t>TVII</t>
+  </si>
+  <si>
+    <t>TVIII</t>
+  </si>
+  <si>
+    <t>TIX</t>
+  </si>
+  <si>
+    <t>TX</t>
+  </si>
+  <si>
+    <t>TXII</t>
+  </si>
+  <si>
+    <t>TXIIIa</t>
+  </si>
+  <si>
+    <t>TXIII</t>
+  </si>
+  <si>
+    <t>TXIV</t>
+  </si>
+  <si>
+    <t>TXV</t>
+  </si>
+  <si>
+    <t>TXVI</t>
+  </si>
+  <si>
+    <t>TXVII</t>
+  </si>
+  <si>
+    <t>TXVIII</t>
+  </si>
+  <si>
+    <t>TXIX</t>
+  </si>
+  <si>
+    <t>TXX</t>
+  </si>
+  <si>
+    <t>TXXI</t>
+  </si>
+  <si>
+    <t>TXXII</t>
   </si>
   <si>
     <t>Proxy/Variable</t>
@@ -316,7 +316,7 @@
     <t xml:space="preserve">Ding et al. (2002)</t>
   </si>
   <si>
-    <t xml:space="preserve">Mean size (μm)</t>
+    <t xml:space="preserve">Mean loess size (μm)</t>
   </si>
   <si>
     <t xml:space="preserve">Gulang Loess</t>
@@ -334,10 +334,10 @@
     <t xml:space="preserve">Inorganic loess carbonates δ13C (‰)</t>
   </si>
   <si>
-    <t xml:space="preserve">MAP (mm/day)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAT (°C)</t>
+    <t xml:space="preserve">Mean Annual Precipitation (mm/day)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mean Annual Temperature (°C)</t>
   </si>
   <si>
     <t xml:space="preserve">Zoige Basin</t>
@@ -346,7 +346,8 @@
     <t xml:space="preserve">Zhao et al. (2021)</t>
   </si>
   <si>
-    <t xml:space="preserve">AP (%) (excl. Gramineae and aquatic/semi-aquatic taxa)</t>
+    <t xml:space="preserve">Arboreal pollen (AP %) 
+(excl. Gramineae and aquatic/semi-aquatic taxa)</t>
   </si>
   <si>
     <t xml:space="preserve">Tenaghi Philippon</t>
@@ -355,7 +356,8 @@
     <t xml:space="preserve">Tzedakis et al. (2006)</t>
   </si>
   <si>
-    <t xml:space="preserve">AP (%) (excl. Pinus)</t>
+    <t xml:space="preserve">Arboreal pollen (AP %) 
+(excl. Pinus)</t>
   </si>
   <si>
     <t xml:space="preserve">Lake Ohrid</t>
@@ -364,13 +366,14 @@
     <t xml:space="preserve">Donders et al. (2021)</t>
   </si>
   <si>
-    <t xml:space="preserve">AP (%)</t>
+    <t xml:space="preserve">Arboreal pollen (AP %)</t>
   </si>
   <si>
     <t xml:space="preserve">Zhao et al. (2020)</t>
   </si>
   <si>
-    <t xml:space="preserve">AP (%) (excl. Quercus &amp; Alnus)</t>
+    <t xml:space="preserve">Arboreal pollen (AP %) 
+(excl. Quercus &amp; Alnus)</t>
   </si>
   <si>
     <t>Funza09</t>
@@ -1867,7 +1870,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="260">
+  <cellXfs count="261">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" quotePrefix="0" pivotButton="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
@@ -2153,6 +2156,9 @@
     <xf fontId="3" fillId="197" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
     <xf fontId="4" fillId="198" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
     <xf fontId="3" fillId="199" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
+    <xf fontId="2" fillId="0" borderId="19" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf fontId="4" fillId="200" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
     <xf fontId="4" fillId="201" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
     <xf fontId="4" fillId="202" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
@@ -4729,9 +4735,9 @@
         <v>3.4122222222222218</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="28.5">
       <c r="A25" s="201"/>
-      <c r="B25" s="214" t="s">
+      <c r="B25" s="226" t="s">
         <v>91</v>
       </c>
       <c r="C25" s="36" t="s">
@@ -4740,19 +4746,19 @@
       <c r="D25" s="37" t="s">
         <v>93</v>
       </c>
-      <c r="E25" s="226">
+      <c r="E25" s="227">
         <v>97.390000000000001</v>
       </c>
-      <c r="F25" s="227">
+      <c r="F25" s="228">
         <v>95.410000000000011</v>
       </c>
-      <c r="G25" s="228">
+      <c r="G25" s="229">
         <v>91.740000000000009</v>
       </c>
-      <c r="H25" s="229">
+      <c r="H25" s="230">
         <v>96.260000000000005</v>
       </c>
-      <c r="I25" s="230">
+      <c r="I25" s="231">
         <v>92.290000000000006</v>
       </c>
       <c r="J25" s="16">
@@ -4776,7 +4782,7 @@
       <c r="P25" s="151">
         <v>88.310000000000002</v>
       </c>
-      <c r="Q25" s="231">
+      <c r="Q25" s="232">
         <v>89.650000000000006</v>
       </c>
       <c r="R25" s="24">
@@ -4794,22 +4800,22 @@
       <c r="V25" s="102">
         <v>59.25</v>
       </c>
-      <c r="W25" s="232">
+      <c r="W25" s="233">
         <v>83.149999999999991</v>
       </c>
       <c r="X25" s="86">
         <v>69.789999999999992</v>
       </c>
-      <c r="Y25" s="233">
+      <c r="Y25" s="234">
         <v>67.480000000000004</v>
       </c>
-      <c r="Z25" s="234"/>
-      <c r="AA25" s="234"/>
-      <c r="AB25" s="234"/>
+      <c r="Z25" s="235"/>
+      <c r="AA25" s="235"/>
+      <c r="AB25" s="235"/>
     </row>
-    <row r="26">
+    <row r="26" ht="28.5">
       <c r="A26" s="201"/>
-      <c r="B26" s="214" t="s">
+      <c r="B26" s="226" t="s">
         <v>94</v>
       </c>
       <c r="C26" s="36" t="s">
@@ -4821,10 +4827,10 @@
       <c r="E26" s="171">
         <v>72.732200000000006</v>
       </c>
-      <c r="F26" s="235">
+      <c r="F26" s="236">
         <v>83.296330000000012</v>
       </c>
-      <c r="G26" s="236">
+      <c r="G26" s="237">
         <v>80.017300000000006</v>
       </c>
       <c r="H26" s="127">
@@ -4833,7 +4839,7 @@
       <c r="I26" s="182">
         <v>80.170400000000001</v>
       </c>
-      <c r="J26" s="237">
+      <c r="J26" s="238">
         <v>79.309809999999999</v>
       </c>
       <c r="K26" s="16">
@@ -4851,7 +4857,7 @@
       <c r="O26" s="135">
         <v>73.829080000000005</v>
       </c>
-      <c r="P26" s="226">
+      <c r="P26" s="227">
         <v>83.376289999999997</v>
       </c>
       <c r="Q26" s="62">
@@ -4866,7 +4872,7 @@
       <c r="T26" s="48">
         <v>63.313799999999993</v>
       </c>
-      <c r="U26" s="238">
+      <c r="U26" s="239">
         <v>74.11099999999999</v>
       </c>
       <c r="V26" s="85">
@@ -4881,9 +4887,9 @@
       <c r="Y26" s="151">
         <v>78.379899999999992</v>
       </c>
-      <c r="Z26" s="234"/>
-      <c r="AA26" s="234"/>
-      <c r="AB26" s="234"/>
+      <c r="Z26" s="235"/>
+      <c r="AA26" s="235"/>
+      <c r="AB26" s="235"/>
     </row>
     <row r="27">
       <c r="A27" s="201"/>
@@ -4899,7 +4905,7 @@
       <c r="E27" s="113">
         <v>48.869999999999997</v>
       </c>
-      <c r="F27" s="239">
+      <c r="F27" s="240">
         <v>84.419999999999987</v>
       </c>
       <c r="G27" s="24">
@@ -4911,7 +4917,7 @@
       <c r="I27" s="41">
         <v>62.209999999999987</v>
       </c>
-      <c r="J27" s="240">
+      <c r="J27" s="241">
         <v>77.850000000000009</v>
       </c>
       <c r="K27" s="135">
@@ -4926,7 +4932,7 @@
       <c r="N27" s="73">
         <v>84.640000000000001</v>
       </c>
-      <c r="O27" s="241">
+      <c r="O27" s="242">
         <v>63.18</v>
       </c>
       <c r="P27" s="212">
@@ -4950,7 +4956,7 @@
       <c r="V27" s="135">
         <v>73.829999999999998</v>
       </c>
-      <c r="W27" s="242">
+      <c r="W27" s="243">
         <v>73.189999999999998</v>
       </c>
       <c r="X27" s="175">
@@ -4969,9 +4975,9 @@
         <v>82.549999999999997</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="28.5">
       <c r="A28" s="201"/>
-      <c r="B28" s="214" t="s">
+      <c r="B28" s="226" t="s">
         <v>99</v>
       </c>
       <c r="C28" s="36" t="s">
@@ -4980,7 +4986,7 @@
       <c r="D28" s="37" t="s">
         <v>101</v>
       </c>
-      <c r="E28" s="234"/>
+      <c r="E28" s="235"/>
       <c r="F28" s="16">
         <v>57.750000000000007</v>
       </c>
@@ -4990,7 +4996,7 @@
       <c r="H28" s="112">
         <v>41.819999999999993</v>
       </c>
-      <c r="I28" s="243">
+      <c r="I28" s="244">
         <v>43.68</v>
       </c>
       <c r="J28" s="47">
@@ -5011,7 +5017,7 @@
       <c r="O28" s="81">
         <v>41.029999999999987</v>
       </c>
-      <c r="P28" s="244">
+      <c r="P28" s="245">
         <v>39.369999999999997</v>
       </c>
       <c r="Q28" s="52">
@@ -5038,7 +5044,7 @@
       <c r="X28" s="158">
         <v>20.719999999999999</v>
       </c>
-      <c r="Y28" s="245">
+      <c r="Y28" s="246">
         <v>24.059999999999999</v>
       </c>
       <c r="Z28" s="24">
@@ -5071,7 +5077,7 @@
       <c r="G29" s="133">
         <v>0.41999999999999998</v>
       </c>
-      <c r="H29" s="246">
+      <c r="H29" s="247">
         <v>0.47999999999999998</v>
       </c>
       <c r="I29" s="110">
@@ -5080,7 +5086,7 @@
       <c r="J29" s="16">
         <v>2</v>
       </c>
-      <c r="K29" s="247">
+      <c r="K29" s="248">
         <v>0.46000000000000002</v>
       </c>
       <c r="L29" s="167">
@@ -5089,7 +5095,7 @@
       <c r="M29" s="114">
         <v>0.69000000000000006</v>
       </c>
-      <c r="N29" s="248">
+      <c r="N29" s="249">
         <v>0.95000000000000007</v>
       </c>
       <c r="O29" s="78">
@@ -5104,7 +5110,7 @@
       <c r="R29" s="24">
         <v>0.39000000000000001</v>
       </c>
-      <c r="S29" s="246">
+      <c r="S29" s="247">
         <v>0.47999999999999998</v>
       </c>
       <c r="T29" s="171">
@@ -5146,20 +5152,20 @@
       <c r="D30" s="37" t="s">
         <v>107</v>
       </c>
-      <c r="E30" s="234"/>
+      <c r="E30" s="235"/>
       <c r="F30" s="123">
         <v>41.299999999999997</v>
       </c>
       <c r="G30" s="174">
         <v>37.600000000000001</v>
       </c>
-      <c r="H30" s="244">
+      <c r="H30" s="245">
         <v>29.600000000000001</v>
       </c>
       <c r="I30" s="127">
         <v>39.799999999999997</v>
       </c>
-      <c r="J30" s="249">
+      <c r="J30" s="250">
         <v>43.700000000000003</v>
       </c>
       <c r="K30" s="112">
@@ -5177,10 +5183,10 @@
       <c r="O30" s="221">
         <v>34.200000000000003</v>
       </c>
-      <c r="P30" s="250">
+      <c r="P30" s="251">
         <v>44</v>
       </c>
-      <c r="Q30" s="251">
+      <c r="Q30" s="252">
         <v>40.899999999999999</v>
       </c>
       <c r="R30" s="152">
@@ -5189,7 +5195,7 @@
       <c r="S30" s="97">
         <v>24</v>
       </c>
-      <c r="T30" s="252">
+      <c r="T30" s="253">
         <v>43.299999999999997</v>
       </c>
       <c r="U30" s="24">
@@ -5210,16 +5216,16 @@
       <c r="Z30" s="140">
         <v>16</v>
       </c>
-      <c r="AA30" s="253">
+      <c r="AA30" s="254">
         <v>36.099999999999987</v>
       </c>
-      <c r="AB30" s="243">
+      <c r="AB30" s="244">
         <v>34</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="254"/>
-      <c r="B31" s="255" t="s">
+      <c r="A31" s="255"/>
+      <c r="B31" s="256" t="s">
         <v>108</v>
       </c>
       <c r="C31" s="91" t="s">
@@ -5228,7 +5234,7 @@
       <c r="D31" s="92" t="s">
         <v>83</v>
       </c>
-      <c r="E31" s="256">
+      <c r="E31" s="257">
         <v>5.8192583240551201</v>
       </c>
       <c r="F31" s="175">
@@ -5237,7 +5243,7 @@
       <c r="G31" s="23">
         <v>5.4540993681073786</v>
       </c>
-      <c r="H31" s="241">
+      <c r="H31" s="242">
         <v>5.3526061699153864</v>
       </c>
       <c r="I31" s="222">
@@ -5255,31 +5261,31 @@
       <c r="M31" s="16">
         <v>7.1205598525011666</v>
       </c>
-      <c r="N31" s="230">
+      <c r="N31" s="231">
         <v>6.7392051262721004</v>
       </c>
-      <c r="O31" s="236">
+      <c r="O31" s="237">
         <v>6.6926350104367964</v>
       </c>
-      <c r="P31" s="229">
+      <c r="P31" s="230">
         <v>6.9377300834483604</v>
       </c>
-      <c r="Q31" s="238">
+      <c r="Q31" s="239">
         <v>6.1541501293850773</v>
       </c>
-      <c r="R31" s="257">
+      <c r="R31" s="258">
         <v>4.6118147287067597</v>
       </c>
       <c r="S31" s="135">
         <v>6.128081452416362</v>
       </c>
-      <c r="T31" s="239">
+      <c r="T31" s="240">
         <v>6.9137373506596838</v>
       </c>
-      <c r="U31" s="258">
+      <c r="U31" s="259">
         <v>5.9610053396232736</v>
       </c>
-      <c r="V31" s="249">
+      <c r="V31" s="250">
         <v>6.7565447172132354</v>
       </c>
       <c r="W31" s="172">
@@ -5288,12 +5294,12 @@
       <c r="X31" s="21">
         <v>5.4184679676784988</v>
       </c>
-      <c r="Y31" s="259">
+      <c r="Y31" s="260">
         <v>5.3153149429166078</v>
       </c>
-      <c r="Z31" s="234"/>
-      <c r="AA31" s="234"/>
-      <c r="AB31" s="234"/>
+      <c r="Z31" s="235"/>
+      <c r="AA31" s="235"/>
+      <c r="AB31" s="235"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/Figures/Heatmaps/Amp-heatmap.xlsx
+++ b/Figures/Heatmaps/Amp-heatmap.xlsx
@@ -118,7 +118,7 @@
     <t xml:space="preserve">MIS 12/MIS 11c</t>
   </si>
   <si>
-    <t xml:space="preserve">MIS 14/MIS 13a</t>
+    <t xml:space="preserve">MIS 13b-14/MIS 13a</t>
   </si>
   <si>
     <t xml:space="preserve">MIS 15b/MIS 15a</t>
@@ -133,7 +133,7 @@
     <t xml:space="preserve">MIS 20/MIS 19c</t>
   </si>
   <si>
-    <t xml:space="preserve">MIS 22/MIS 21e</t>
+    <t xml:space="preserve">MIS 22-24/MIS 21e</t>
   </si>
   <si>
     <t xml:space="preserve">MIS 26/MIS 25</t>
@@ -292,16 +292,10 @@
     <t xml:space="preserve">Tropical stack</t>
   </si>
   <si>
-    <t xml:space="preserve">Herbert et al. (2010)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ΔMOT (°C)</t>
-  </si>
-  <si>
-    <t>ΔMOT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clark et al. (2025)</t>
+    <t xml:space="preserve">SST (°C)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herbert et al. (2017)</t>
   </si>
   <si>
     <t xml:space="preserve">Terrestrial archives</t>
@@ -344,6 +338,12 @@
   </si>
   <si>
     <t xml:space="preserve">Zhao et al. (2021)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heqing Basin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wang et al. (2025)</t>
   </si>
   <si>
     <t xml:space="preserve">Arboreal pollen (AP %) 
@@ -429,7 +429,7 @@
       <color rgb="FFF1F1F1"/>
     </font>
   </fonts>
-  <fills count="232">
+  <fills count="228">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1254,37 +1254,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF8048AB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9768BA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF8149AC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF9768BA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF834BAC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7232A1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA279C2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCAB2DC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCFBFD"/>
+        <fgColor rgb="FF7131A0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4AAD8"/>
       </patternFill>
     </fill>
     <fill>
@@ -1294,17 +1284,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA57CC3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDFDFE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDFD1EA"/>
+        <fgColor rgb="FF986ABB"/>
       </patternFill>
     </fill>
     <fill>
@@ -1314,7 +1294,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE0D2EB"/>
+        <fgColor rgb="FFD3BFE2"/>
       </patternFill>
     </fill>
     <fill>
@@ -1325,6 +1305,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFDFDFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFB28FCC"/>
       </patternFill>
     </fill>
@@ -1365,11 +1350,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF7131A0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFE9DFF0"/>
       </patternFill>
     </fill>
@@ -1390,22 +1370,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA279C2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFAC87C8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF9363B7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFAB86C7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA075C0"/>
+        <fgColor rgb="FFF7F3F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC1A5D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -1415,57 +1400,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC1A5D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF8E5CB4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD3BFE2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7537A3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7A3EA6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8148AB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF773BA5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8047AA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF854FAE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9362B7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB492CD"/>
       </patternFill>
     </fill>
     <fill>
@@ -1476,6 +1411,56 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC5ABD9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7537A3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7A3EA6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8148AB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF773BA5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8047AA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF854FAE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF834BAC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9362B7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB492CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF7638A4"/>
       </patternFill>
     </fill>
@@ -1491,11 +1476,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF986ABB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF783CA6"/>
       </patternFill>
     </fill>
@@ -1521,11 +1501,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFCAB2DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFAF8CCA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDFD1EA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE4D8ED"/>
       </patternFill>
     </fill>
@@ -1551,6 +1541,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA075C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF7E44A9"/>
       </patternFill>
     </fill>
@@ -1561,36 +1556,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF8048AB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF996BBB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA780C5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDAC9E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA177C0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC9ED3"/>
+        <fgColor rgb="FFA57DC3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9B6FBD"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="20">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -1771,21 +1751,6 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin">
         <color auto="1"/>
       </left>
       <right style="thin">
@@ -1870,7 +1835,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="261">
+  <cellXfs count="255">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" quotePrefix="0" pivotButton="0"/>
     <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
@@ -1903,29 +1868,75 @@
     <xf fontId="3" fillId="0" borderId="7" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf fontId="4" fillId="3" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="4" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="5" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="6" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="7" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="8" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="9" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="10" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="11" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="12" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="13" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="14" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="15" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="16" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="17" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="18" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="19" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="20" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="21" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="22" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="23" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="24" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="25" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
+    <xf fontId="4" fillId="3" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="4" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="5" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="6" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="7" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="8" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="9" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="10" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="11" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="12" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="13" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="14" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="15" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="16" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="17" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="18" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="19" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="20" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="21" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="22" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="23" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="24" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="25" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf fontId="0" fillId="2" borderId="8" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center" textRotation="90" vertical="center"/>
     </xf>
@@ -1938,58 +1949,162 @@
     <xf fontId="3" fillId="0" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf fontId="4" fillId="26" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="27" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="28" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="29" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="30" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="31" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="32" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="33" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="34" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="35" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="36" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="37" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="38" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="39" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="40" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="41" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="42" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="43" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="44" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="45" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="46" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="47" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="48" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="49" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="50" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="51" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="52" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="53" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="54" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="55" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="56" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="57" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="58" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="59" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="60" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="61" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="62" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="63" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="64" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="65" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="66" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="67" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="68" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="69" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="70" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="71" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="72" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="73" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="74" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="75" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="76" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="77" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
+    <xf fontId="4" fillId="26" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="27" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="28" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="29" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="30" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="31" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="32" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="33" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="34" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="35" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="36" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="37" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="38" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="39" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="40" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="41" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="42" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="43" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="44" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="45" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="46" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="47" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="48" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="49" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="50" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="51" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="52" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="53" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="54" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="55" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="56" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="57" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="58" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="59" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="60" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="61" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="62" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="63" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="64" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="65" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="66" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="67" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="68" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="69" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="70" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="71" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="72" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="73" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="74" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="75" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="76" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="77" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf fontId="2" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1999,206 +2114,492 @@
     <xf fontId="3" fillId="0" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf fontId="4" fillId="78" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="79" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="80" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="81" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="82" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="83" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="84" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="85" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="86" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="87" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="88" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="89" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
+    <xf fontId="4" fillId="78" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="79" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="80" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="81" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="82" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="83" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="84" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="85" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="86" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="87" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="88" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="89" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="11" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf fontId="3" fillId="0" borderId="11" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf fontId="4" fillId="90" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="91" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="92" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="93" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="94" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="95" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="96" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="97" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="98" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="99" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="100" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="101" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="102" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="103" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="104" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="105" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="106" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="107" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="108" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="109" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="110" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="111" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="112" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="113" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="114" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="115" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="116" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="117" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="118" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="119" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="120" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="121" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="122" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="123" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="124" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="125" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="126" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="127" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="128" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="129" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="130" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="131" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="132" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="133" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="134" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="135" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="136" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="137" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="138" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="139" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="140" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="141" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="142" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="143" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="144" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="145" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="146" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="147" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="148" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="149" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="150" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="151" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="152" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="153" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="154" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="155" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="156" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="157" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="158" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="159" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="160" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="161" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="162" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="163" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="164" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="165" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="166" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="167" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="168" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="169" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="170" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
+    <xf fontId="4" fillId="90" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="91" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="92" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="93" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="94" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="95" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="96" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="97" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="98" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="99" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="100" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="101" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="102" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="103" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="104" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="105" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="106" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="107" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="108" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="109" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="110" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="111" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="112" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="113" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="114" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="115" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="116" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="117" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="118" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="119" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="120" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="121" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="122" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="123" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="124" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="125" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="126" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="127" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="128" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="129" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="130" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="131" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="132" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="133" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="134" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="135" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="136" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="137" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="138" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="139" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="140" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="141" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="142" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="143" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="144" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="145" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="146" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="147" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="148" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="149" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="150" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="151" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="152" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="153" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="154" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="155" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="156" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="157" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="158" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="159" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="160" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="161" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="162" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="163" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="164" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf fontId="0" fillId="2" borderId="12" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center" textRotation="90" vertical="center"/>
     </xf>
     <xf fontId="2" fillId="0" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="14" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf fontId="3" fillId="0" borderId="14" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf fontId="3" fillId="171" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="172" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="173" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="174" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="175" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="176" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="177" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="1" fillId="178" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+    <xf fontId="4" fillId="165" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="166" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="167" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="168" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="169" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="170" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="171" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="172" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="173" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="1" fillId="174" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center" textRotation="90" vertical="center"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="15" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+    <xf fontId="2" fillId="0" borderId="14" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="0" fillId="178" borderId="16" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+    <xf fontId="3" fillId="175" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="174" borderId="15" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center" textRotation="90" vertical="center"/>
+    </xf>
+    <xf fontId="2" fillId="0" borderId="16" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="4" fillId="176" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="177" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="178" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="179" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="180" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="181" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="182" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
     </xf>
     <xf fontId="2" fillId="0" borderId="17" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="4" fillId="179" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="180" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="181" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="182" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="183" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="184" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="185" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
+    <xf fontId="4" fillId="183" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="184" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf fontId="2" fillId="0" borderId="18" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="4" fillId="186" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="187" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="188" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
+    <xf fontId="4" fillId="185" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="186" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="187" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="188" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="189" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="190" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="191" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="192" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="193" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="194" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="195" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="3" fillId="196" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="2" fillId="0" borderId="18" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="197" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="198" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="199" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="200" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="201" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="202" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="203" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="204" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="205" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="206" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="207" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="208" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="209" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="210" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="211" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="212" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="213" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="214" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="215" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="216" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="217" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="218" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="219" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="3" fillId="220" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="221" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="222" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="223" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="224" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="225" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="0" fillId="174" borderId="12" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center" textRotation="90" vertical="center"/>
+    </xf>
     <xf fontId="2" fillId="0" borderId="19" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="4" fillId="189" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="190" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="191" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="192" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="193" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="194" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="195" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="196" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="197" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="198" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="199" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="2" fillId="0" borderId="19" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="200" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="201" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="202" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="203" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="204" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="205" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="206" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="207" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="208" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="4" fillId="209" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="210" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="211" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="212" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="213" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="214" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="215" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="216" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="217" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="218" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="219" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="220" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="221" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="222" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="223" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="224" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="225" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="226" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="227" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="0" fillId="178" borderId="12" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center" textRotation="90" vertical="center"/>
-    </xf>
-    <xf fontId="2" fillId="0" borderId="20" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="4" fillId="228" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="3" fillId="229" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="230" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
-    <xf fontId="4" fillId="231" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" quotePrefix="0" pivotButton="0"/>
+    <xf fontId="4" fillId="226" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf fontId="4" fillId="227" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2733,12 +3134,12 @@
     <col customWidth="1" min="8" max="8" width="15.57421875"/>
     <col customWidth="1" min="9" max="9" width="14.57421875"/>
     <col customWidth="1" min="10" max="10" width="16.00390625"/>
-    <col customWidth="1" min="11" max="11" width="15.421875"/>
+    <col customWidth="1" min="11" max="11" width="19.8515625"/>
     <col customWidth="1" min="12" max="12" width="16.7109375"/>
     <col customWidth="1" min="13" max="13" width="21.140625"/>
     <col customWidth="1" min="14" max="14" width="19.140625"/>
     <col customWidth="1" min="15" max="15" width="17.421875"/>
-    <col customWidth="1" min="16" max="16" width="15.8515625"/>
+    <col customWidth="1" min="16" max="16" width="20.7109375"/>
     <col customWidth="1" min="17" max="17" width="15.57421875"/>
     <col customWidth="1" min="18" max="18" width="15.8515625"/>
     <col customWidth="1" min="19" max="19" width="14.00390625"/>
@@ -3984,760 +4385,752 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="34"/>
-      <c r="B16" s="90"/>
+      <c r="A16" s="182"/>
+      <c r="B16" s="183" t="s">
+        <v>73</v>
+      </c>
       <c r="C16" s="91" t="s">
         <v>72</v>
       </c>
       <c r="D16" s="92" t="s">
-        <v>73</v>
-      </c>
-      <c r="E16" s="182">
-        <v>3.0760000000000001</v>
-      </c>
-      <c r="F16" s="146">
-        <v>2.6739999999999999</v>
-      </c>
-      <c r="G16" s="88">
-        <v>1.389</v>
-      </c>
-      <c r="H16" s="183">
-        <v>2.6480000000000001</v>
-      </c>
-      <c r="I16" s="184">
-        <v>3.0630000000000002</v>
-      </c>
-      <c r="J16" s="185">
-        <v>3.4009999999999998</v>
-      </c>
-      <c r="K16" s="68">
-        <v>1.639</v>
-      </c>
-      <c r="L16" s="31">
-        <v>1.1240000000000001</v>
-      </c>
-      <c r="M16" s="64">
-        <v>1.835</v>
-      </c>
-      <c r="N16" s="96">
-        <v>2.2989999999999999</v>
-      </c>
-      <c r="O16" s="111">
-        <v>2.476</v>
+        <v>74</v>
+      </c>
+      <c r="E16" s="184">
+        <v>3.0650000000000008</v>
+      </c>
+      <c r="F16" s="138">
+        <v>2.652000000000001</v>
+      </c>
+      <c r="G16" s="168">
+        <v>1.3619999999999981</v>
+      </c>
+      <c r="H16" s="185">
+        <v>2.609999999999999</v>
+      </c>
+      <c r="I16" s="186">
+        <v>3.0379999999999998</v>
+      </c>
+      <c r="J16" s="187">
+        <v>3.3739999999999992</v>
+      </c>
+      <c r="K16" s="82">
+        <v>1.600000000000001</v>
+      </c>
+      <c r="L16" s="83">
+        <v>1.1170000000000011</v>
+      </c>
+      <c r="M16" s="118">
+        <v>1.8200000000000001</v>
+      </c>
+      <c r="N16" s="144">
+        <v>2.2539999999999978</v>
+      </c>
+      <c r="O16" s="109">
+        <v>2.4620000000000002</v>
       </c>
       <c r="P16" s="16">
-        <v>3.4409999999999998</v>
-      </c>
-      <c r="Q16" s="48">
-        <v>1.7829999999999999</v>
+        <v>3.3960000000000008</v>
+      </c>
+      <c r="Q16" s="126">
+        <v>1.7739999999999969</v>
       </c>
       <c r="R16" s="157">
-        <v>0.79399999999999993</v>
-      </c>
-      <c r="S16" s="64">
-        <v>1.8420000000000001</v>
-      </c>
-      <c r="T16" s="126">
-        <v>1.8089999999999999</v>
-      </c>
-      <c r="U16" s="102">
-        <v>1.714</v>
-      </c>
-      <c r="V16" s="41">
-        <v>1.8660000000000001</v>
-      </c>
-      <c r="W16" s="186">
-        <v>2.4039999999999999</v>
+        <v>0.7710000000000008</v>
+      </c>
+      <c r="S16" s="118">
+        <v>1.821999999999999</v>
+      </c>
+      <c r="T16" s="14">
+        <v>1.794</v>
+      </c>
+      <c r="U16" s="188">
+        <v>1.701999999999998</v>
+      </c>
+      <c r="V16" s="189">
+        <v>1.8410000000000011</v>
+      </c>
+      <c r="W16" s="173">
+        <v>2.3819999999999979</v>
       </c>
       <c r="X16" s="24">
-        <v>0.52100000000000002</v>
-      </c>
-      <c r="Y16" s="187">
-        <v>1.613</v>
-      </c>
-      <c r="Z16" s="135">
-        <v>2.5859999999999999</v>
-      </c>
-      <c r="AA16" s="49">
-        <v>0.76700000000000002</v>
-      </c>
-      <c r="AB16" s="71">
-        <v>1.4159999999999999</v>
+        <v>0.50499999999999901</v>
+      </c>
+      <c r="Y16" s="82">
+        <v>1.597999999999999</v>
+      </c>
+      <c r="Z16" s="190">
+        <v>2.573</v>
+      </c>
+      <c r="AA16" s="191">
+        <v>0.75600000000000023</v>
+      </c>
+      <c r="AB16" s="192">
+        <v>1.4050000000000009</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="188"/>
-      <c r="B17" s="189" t="s">
-        <v>74</v>
-      </c>
-      <c r="C17" s="190" t="s">
+      <c r="A17" s="193" t="s">
         <v>75</v>
       </c>
-      <c r="D17" s="191" t="s">
+      <c r="B17" s="194" t="s">
         <v>76</v>
       </c>
-      <c r="E17" s="138">
-        <v>3.4300000000000002</v>
-      </c>
-      <c r="F17" s="59">
-        <v>3.7000000000000002</v>
-      </c>
-      <c r="G17" s="140">
-        <v>1.3600000000000001</v>
-      </c>
-      <c r="H17" s="75">
-        <v>2.4100000000000001</v>
-      </c>
-      <c r="I17" s="164">
-        <v>3.1899999999999999</v>
-      </c>
-      <c r="J17" s="16">
-        <v>4.4700000000000006</v>
-      </c>
-      <c r="K17" s="101">
-        <v>1.8500000000000001</v>
-      </c>
-      <c r="L17" s="192">
-        <v>0.47999999999999998</v>
-      </c>
-      <c r="M17" s="193">
-        <v>2.2799999999999998</v>
-      </c>
-      <c r="N17" s="82">
-        <v>1.9299999999999999</v>
-      </c>
-      <c r="O17" s="171">
-        <v>3.1699999999999999</v>
-      </c>
-      <c r="P17" s="194">
-        <v>2.96</v>
-      </c>
-      <c r="Q17" s="113">
-        <v>1.082866975</v>
-      </c>
-      <c r="R17" s="195">
-        <v>0.45066682400000002</v>
-      </c>
-      <c r="S17" s="167">
-        <v>1.0632090009999999</v>
-      </c>
-      <c r="T17" s="50">
-        <v>1.5592512430000001</v>
-      </c>
-      <c r="U17" s="83">
-        <v>1.2561845890000001</v>
-      </c>
-      <c r="V17" s="196">
-        <v>1.30328504</v>
-      </c>
-      <c r="W17" s="74">
-        <v>1.6200860530000001</v>
-      </c>
-      <c r="X17" s="133">
-        <v>0.454125944</v>
-      </c>
-      <c r="Y17" s="197">
-        <v>0.75416003700000001</v>
-      </c>
-      <c r="Z17" s="198">
-        <v>1.2724866029999999</v>
-      </c>
-      <c r="AA17" s="24">
-        <v>0.38756779699999999</v>
-      </c>
-      <c r="AB17" s="163">
-        <v>0.95791995500000005</v>
+      <c r="C17" s="105" t="s">
+        <v>77</v>
+      </c>
+      <c r="D17" s="106" t="s">
+        <v>78</v>
+      </c>
+      <c r="E17" s="88">
+        <v>0.46543508</v>
+      </c>
+      <c r="F17" s="94">
+        <v>0.93796140000000006</v>
+      </c>
+      <c r="G17" s="101">
+        <v>0.53222311999999994</v>
+      </c>
+      <c r="H17" s="140">
+        <v>0.39315810000000001</v>
+      </c>
+      <c r="I17" s="80">
+        <v>0.74460988000000006</v>
+      </c>
+      <c r="J17" s="41">
+        <v>0.65004404999999998</v>
+      </c>
+      <c r="K17" s="55">
+        <v>0.20310690000000001</v>
+      </c>
+      <c r="L17" s="100">
+        <v>0.20829890000000009</v>
+      </c>
+      <c r="M17" s="63">
+        <v>0.78860586999999993</v>
+      </c>
+      <c r="N17" s="117">
+        <v>0.48935040000000002</v>
+      </c>
+      <c r="O17" s="83">
+        <v>0.36399880000000001</v>
+      </c>
+      <c r="P17" s="162">
+        <v>1.0881101</v>
+      </c>
+      <c r="Q17" s="67">
+        <v>0.28141860000000007</v>
+      </c>
+      <c r="R17" s="24">
+        <v>0.1168252</v>
+      </c>
+      <c r="S17" s="120">
+        <v>0.16388240000000001</v>
+      </c>
+      <c r="T17" s="195">
+        <v>0.13180549999999999</v>
+      </c>
+      <c r="U17" s="71">
+        <v>0.47601890000000002</v>
+      </c>
+      <c r="V17" s="84">
+        <v>0.40267150000000002</v>
+      </c>
+      <c r="W17" s="16">
+        <v>1.2833364</v>
+      </c>
+      <c r="X17" s="113">
+        <v>0.31718449999999992</v>
+      </c>
+      <c r="Y17" s="95">
+        <v>0.26624639999999999</v>
+      </c>
+      <c r="Z17" s="157">
+        <v>0.22978309999999991</v>
+      </c>
+      <c r="AA17" s="54">
+        <v>0.17314460000000001</v>
+      </c>
+      <c r="AB17" s="31">
+        <v>0.35667420000000011</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="199" t="s">
-        <v>77</v>
-      </c>
-      <c r="B18" s="200" t="s">
-        <v>78</v>
-      </c>
-      <c r="C18" s="105" t="s">
+      <c r="A18" s="196"/>
+      <c r="B18" s="197" t="s">
         <v>79</v>
       </c>
-      <c r="D18" s="106" t="s">
+      <c r="C18" s="36" t="s">
         <v>80</v>
       </c>
-      <c r="E18" s="88">
-        <v>0.46543508</v>
-      </c>
-      <c r="F18" s="94">
-        <v>0.93796140000000006</v>
-      </c>
-      <c r="G18" s="101">
-        <v>0.53222311999999994</v>
-      </c>
-      <c r="H18" s="140">
-        <v>0.39315810000000001</v>
-      </c>
-      <c r="I18" s="80">
-        <v>0.74460988000000006</v>
-      </c>
-      <c r="J18" s="41">
-        <v>0.65004404999999998</v>
-      </c>
-      <c r="K18" s="55">
-        <v>0.20310690000000001</v>
-      </c>
-      <c r="L18" s="100">
-        <v>0.20829890000000009</v>
-      </c>
-      <c r="M18" s="63">
-        <v>0.78860586999999993</v>
-      </c>
-      <c r="N18" s="117">
-        <v>0.48935040000000002</v>
-      </c>
-      <c r="O18" s="83">
-        <v>0.36399880000000001</v>
-      </c>
-      <c r="P18" s="162">
-        <v>1.0881101</v>
-      </c>
-      <c r="Q18" s="67">
-        <v>0.28141860000000007</v>
-      </c>
-      <c r="R18" s="24">
-        <v>0.1168252</v>
-      </c>
-      <c r="S18" s="120">
-        <v>0.16388240000000001</v>
-      </c>
-      <c r="T18" s="195">
-        <v>0.13180549999999999</v>
-      </c>
-      <c r="U18" s="71">
-        <v>0.47601890000000002</v>
-      </c>
-      <c r="V18" s="84">
-        <v>0.40267150000000002</v>
-      </c>
-      <c r="W18" s="16">
-        <v>1.2833364</v>
-      </c>
-      <c r="X18" s="113">
-        <v>0.31718449999999992</v>
-      </c>
-      <c r="Y18" s="95">
-        <v>0.26624639999999999</v>
-      </c>
-      <c r="Z18" s="157">
-        <v>0.22978309999999991</v>
-      </c>
-      <c r="AA18" s="54">
-        <v>0.17314460000000001</v>
-      </c>
-      <c r="AB18" s="31">
-        <v>0.35667420000000011</v>
+      <c r="D18" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="E18" s="198">
+        <v>27.065999999999999</v>
+      </c>
+      <c r="F18" s="199">
+        <v>30.209</v>
+      </c>
+      <c r="G18" s="126">
+        <v>23.931999999999999</v>
+      </c>
+      <c r="H18" s="74">
+        <v>19.559000000000001</v>
+      </c>
+      <c r="I18" s="47">
+        <v>25.966000000000001</v>
+      </c>
+      <c r="J18" s="134">
+        <v>24.015999999999998</v>
+      </c>
+      <c r="K18" s="18">
+        <v>18.419</v>
+      </c>
+      <c r="L18" s="140">
+        <v>17.495999999999999</v>
+      </c>
+      <c r="M18" s="16">
+        <v>41.530000000000001</v>
+      </c>
+      <c r="N18" s="124">
+        <v>23.132999999999999</v>
+      </c>
+      <c r="O18" s="43">
+        <v>19.891999999999999</v>
+      </c>
+      <c r="P18" s="200">
+        <v>36.706000000000003</v>
+      </c>
+      <c r="Q18" s="55">
+        <v>12.382</v>
+      </c>
+      <c r="R18" s="67">
+        <v>14.519</v>
+      </c>
+      <c r="S18" s="24">
+        <v>10.047000000000001</v>
+      </c>
+      <c r="T18" s="201">
+        <v>18.399000000000001</v>
+      </c>
+      <c r="U18" s="202">
+        <v>34.25</v>
+      </c>
+      <c r="V18" s="166">
+        <v>13.324</v>
+      </c>
+      <c r="W18" s="33">
+        <v>21.439</v>
+      </c>
+      <c r="X18" s="203">
+        <v>15.666</v>
+      </c>
+      <c r="Y18" s="204">
+        <v>11.276</v>
+      </c>
+      <c r="Z18" s="167">
+        <v>15.303000000000001</v>
+      </c>
+      <c r="AA18" s="119">
+        <v>15.545</v>
+      </c>
+      <c r="AB18" s="44">
+        <v>17.004000000000001</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="201"/>
-      <c r="B19" s="202" t="s">
-        <v>81</v>
-      </c>
+      <c r="A19" s="196"/>
+      <c r="B19" s="205"/>
       <c r="C19" s="36" t="s">
         <v>82</v>
       </c>
       <c r="D19" s="37" t="s">
         <v>83</v>
       </c>
-      <c r="E19" s="203">
-        <v>27.065999999999999</v>
-      </c>
-      <c r="F19" s="204">
-        <v>30.209</v>
-      </c>
-      <c r="G19" s="126">
-        <v>23.931999999999999</v>
-      </c>
-      <c r="H19" s="74">
-        <v>19.559000000000001</v>
-      </c>
-      <c r="I19" s="47">
-        <v>25.966000000000001</v>
-      </c>
-      <c r="J19" s="134">
-        <v>24.015999999999998</v>
-      </c>
-      <c r="K19" s="18">
-        <v>18.419</v>
-      </c>
-      <c r="L19" s="140">
-        <v>17.495999999999999</v>
-      </c>
-      <c r="M19" s="16">
-        <v>41.530000000000001</v>
-      </c>
-      <c r="N19" s="124">
-        <v>23.132999999999999</v>
-      </c>
-      <c r="O19" s="43">
-        <v>19.891999999999999</v>
-      </c>
-      <c r="P19" s="205">
-        <v>36.706000000000003</v>
-      </c>
-      <c r="Q19" s="55">
-        <v>12.382</v>
-      </c>
-      <c r="R19" s="67">
-        <v>14.519</v>
-      </c>
-      <c r="S19" s="24">
-        <v>10.047000000000001</v>
-      </c>
-      <c r="T19" s="206">
-        <v>18.399000000000001</v>
-      </c>
-      <c r="U19" s="207">
-        <v>34.25</v>
-      </c>
-      <c r="V19" s="166">
-        <v>13.324</v>
-      </c>
-      <c r="W19" s="33">
-        <v>21.439</v>
-      </c>
-      <c r="X19" s="208">
-        <v>15.666</v>
-      </c>
-      <c r="Y19" s="209">
-        <v>11.276</v>
-      </c>
-      <c r="Z19" s="167">
-        <v>15.303000000000001</v>
-      </c>
-      <c r="AA19" s="119">
-        <v>15.545</v>
-      </c>
-      <c r="AB19" s="44">
-        <v>17.004000000000001</v>
+      <c r="E19" s="198">
+        <v>20.971</v>
+      </c>
+      <c r="F19" s="98">
+        <v>21.538</v>
+      </c>
+      <c r="G19" s="45">
+        <v>26.925000000000001</v>
+      </c>
+      <c r="H19" s="61">
+        <v>14.086</v>
+      </c>
+      <c r="I19" s="206">
+        <v>26.596</v>
+      </c>
+      <c r="J19" s="143">
+        <v>21.643000000000001</v>
+      </c>
+      <c r="K19" s="32">
+        <v>14.007</v>
+      </c>
+      <c r="L19" s="70">
+        <v>11.249000000000001</v>
+      </c>
+      <c r="M19" s="169">
+        <v>24.466999999999999</v>
+      </c>
+      <c r="N19" s="115">
+        <v>16.367999999999999</v>
+      </c>
+      <c r="O19" s="17">
+        <v>16.878</v>
+      </c>
+      <c r="P19" s="187">
+        <v>31.68</v>
+      </c>
+      <c r="Q19" s="48">
+        <v>18.324999999999999</v>
+      </c>
+      <c r="R19" s="114">
+        <v>12.573</v>
+      </c>
+      <c r="S19" s="114">
+        <v>12.542999999999999</v>
+      </c>
+      <c r="T19" s="74">
+        <v>15.307</v>
+      </c>
+      <c r="U19" s="137">
+        <v>20.766999999999999</v>
+      </c>
+      <c r="V19" s="143">
+        <v>21.626000000000001</v>
+      </c>
+      <c r="W19" s="16">
+        <v>31.841999999999999</v>
+      </c>
+      <c r="X19" s="77">
+        <v>16.132999999999999</v>
+      </c>
+      <c r="Y19" s="24">
+        <v>8.1280000000000001</v>
+      </c>
+      <c r="Z19" s="32">
+        <v>14.045999999999999</v>
+      </c>
+      <c r="AA19" s="102">
+        <v>17.808</v>
+      </c>
+      <c r="AB19" s="207">
+        <v>11.746</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="201"/>
-      <c r="B20" s="210"/>
+      <c r="A20" s="196"/>
+      <c r="B20" s="208" t="s">
+        <v>84</v>
+      </c>
       <c r="C20" s="36" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D20" s="37" t="s">
-        <v>85</v>
-      </c>
-      <c r="E20" s="203">
-        <v>20.971</v>
-      </c>
-      <c r="F20" s="98">
-        <v>21.538</v>
-      </c>
-      <c r="G20" s="45">
-        <v>26.925000000000001</v>
-      </c>
-      <c r="H20" s="61">
-        <v>14.086</v>
-      </c>
-      <c r="I20" s="211">
-        <v>26.596</v>
-      </c>
-      <c r="J20" s="143">
-        <v>21.643000000000001</v>
-      </c>
-      <c r="K20" s="32">
-        <v>14.007</v>
-      </c>
-      <c r="L20" s="70">
-        <v>11.249000000000001</v>
-      </c>
-      <c r="M20" s="169">
-        <v>24.466999999999999</v>
-      </c>
-      <c r="N20" s="115">
-        <v>16.367999999999999</v>
-      </c>
-      <c r="O20" s="17">
-        <v>16.878</v>
-      </c>
-      <c r="P20" s="212">
-        <v>31.68</v>
-      </c>
-      <c r="Q20" s="48">
-        <v>18.324999999999999</v>
-      </c>
-      <c r="R20" s="114">
-        <v>12.573</v>
-      </c>
-      <c r="S20" s="114">
-        <v>12.542999999999999</v>
-      </c>
-      <c r="T20" s="74">
-        <v>15.307</v>
-      </c>
-      <c r="U20" s="137">
-        <v>20.766999999999999</v>
-      </c>
-      <c r="V20" s="143">
-        <v>21.626000000000001</v>
-      </c>
-      <c r="W20" s="16">
-        <v>31.841999999999999</v>
-      </c>
-      <c r="X20" s="77">
-        <v>16.132999999999999</v>
+        <v>83</v>
+      </c>
+      <c r="E20" s="144">
+        <v>5.6299999999999999</v>
+      </c>
+      <c r="F20" s="16">
+        <v>7.25</v>
+      </c>
+      <c r="G20" s="165">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="H20" s="69">
+        <v>5.1399999999999997</v>
+      </c>
+      <c r="I20" s="165">
+        <v>5.1000000000000014</v>
+      </c>
+      <c r="J20" s="86">
+        <v>5.46</v>
+      </c>
+      <c r="K20" s="128">
+        <v>4.8699999999999992</v>
+      </c>
+      <c r="L20" s="159">
+        <v>4.21</v>
+      </c>
+      <c r="M20" s="131">
+        <v>5.5700000000000003</v>
+      </c>
+      <c r="N20" s="185">
+        <v>6.1399999999999997</v>
+      </c>
+      <c r="O20" s="64">
+        <v>5</v>
+      </c>
+      <c r="P20" s="209">
+        <v>5.3900000000000006</v>
+      </c>
+      <c r="Q20" s="89">
+        <v>3.7599999999999998</v>
+      </c>
+      <c r="R20" s="54">
+        <v>3.359999999999999</v>
+      </c>
+      <c r="S20" s="145">
+        <v>4.9100000000000001</v>
+      </c>
+      <c r="T20" s="18">
+        <v>4.25</v>
+      </c>
+      <c r="U20" s="163">
+        <v>3.73</v>
+      </c>
+      <c r="V20" s="134">
+        <v>4.9800000000000004</v>
+      </c>
+      <c r="W20" s="189">
+        <v>5.0499999999999998</v>
+      </c>
+      <c r="X20" s="210">
+        <v>4.1099999999999994</v>
       </c>
       <c r="Y20" s="24">
-        <v>8.1280000000000001</v>
-      </c>
-      <c r="Z20" s="32">
-        <v>14.045999999999999</v>
-      </c>
-      <c r="AA20" s="102">
-        <v>17.808</v>
-      </c>
-      <c r="AB20" s="213">
-        <v>11.746</v>
+        <v>3.1600000000000001</v>
+      </c>
+      <c r="Z20" s="66">
+        <v>4.2900000000000009</v>
+      </c>
+      <c r="AA20" s="20">
+        <v>5.1699999999999999</v>
+      </c>
+      <c r="AB20" s="116">
+        <v>4.2699999999999996</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="201"/>
-      <c r="B21" s="214" t="s">
-        <v>86</v>
+      <c r="A21" s="196"/>
+      <c r="B21" s="208" t="s">
+        <v>85</v>
       </c>
       <c r="C21" s="36" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D21" s="37" t="s">
-        <v>85</v>
-      </c>
-      <c r="E21" s="144">
-        <v>5.6299999999999999</v>
+        <v>83</v>
+      </c>
+      <c r="E21" s="139">
+        <v>0.33000000000000013</v>
       </c>
       <c r="F21" s="16">
-        <v>7.25</v>
-      </c>
-      <c r="G21" s="165">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="H21" s="69">
-        <v>5.1399999999999997</v>
-      </c>
-      <c r="I21" s="165">
-        <v>5.1000000000000014</v>
-      </c>
-      <c r="J21" s="86">
-        <v>5.46</v>
+        <v>0.47999999999999998</v>
+      </c>
+      <c r="G21" s="69">
+        <v>0.31999999999999978</v>
+      </c>
+      <c r="H21" s="211">
+        <v>0.41000000000000009</v>
+      </c>
+      <c r="I21" s="109">
+        <v>0.37999999999999989</v>
+      </c>
+      <c r="J21" s="212">
+        <v>0.36999999999999972</v>
       </c>
       <c r="K21" s="128">
-        <v>4.8699999999999992</v>
-      </c>
-      <c r="L21" s="159">
-        <v>4.21</v>
-      </c>
-      <c r="M21" s="131">
-        <v>5.5700000000000003</v>
-      </c>
-      <c r="N21" s="183">
-        <v>6.1399999999999997</v>
-      </c>
-      <c r="O21" s="64">
-        <v>5</v>
-      </c>
-      <c r="P21" s="215">
-        <v>5.3900000000000006</v>
-      </c>
-      <c r="Q21" s="89">
-        <v>3.7599999999999998</v>
-      </c>
-      <c r="R21" s="54">
-        <v>3.359999999999999</v>
-      </c>
-      <c r="S21" s="145">
-        <v>4.9100000000000001</v>
-      </c>
-      <c r="T21" s="18">
-        <v>4.25</v>
-      </c>
-      <c r="U21" s="163">
-        <v>3.73</v>
-      </c>
-      <c r="V21" s="134">
-        <v>4.9800000000000004</v>
-      </c>
-      <c r="W21" s="193">
-        <v>5.0499999999999998</v>
-      </c>
-      <c r="X21" s="216">
-        <v>4.1099999999999994</v>
-      </c>
-      <c r="Y21" s="24">
-        <v>3.1600000000000001</v>
-      </c>
-      <c r="Z21" s="66">
-        <v>4.2900000000000009</v>
-      </c>
-      <c r="AA21" s="20">
-        <v>5.1699999999999999</v>
-      </c>
-      <c r="AB21" s="116">
-        <v>4.2699999999999996</v>
+        <v>0.29999999999999982</v>
+      </c>
+      <c r="L21" s="64">
+        <v>0.31000000000000011</v>
+      </c>
+      <c r="M21" s="213">
+        <v>0.35000000000000009</v>
+      </c>
+      <c r="N21" s="181">
+        <v>0.33999999999999991</v>
+      </c>
+      <c r="O21" s="69">
+        <v>0.31999999999999978</v>
+      </c>
+      <c r="P21" s="136">
+        <v>0.36000000000000032</v>
+      </c>
+      <c r="Q21" s="135">
+        <v>0.39000000000000012</v>
+      </c>
+      <c r="R21" s="64">
+        <v>0.30999999999999961</v>
+      </c>
+      <c r="S21" s="121">
+        <v>0.27000000000000002</v>
+      </c>
+      <c r="T21" s="179">
+        <v>0.41999999999999987</v>
+      </c>
+      <c r="U21" s="24">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="V21" s="139">
+        <v>0.33000000000000013</v>
+      </c>
+      <c r="W21" s="121">
+        <v>0.27000000000000002</v>
+      </c>
+      <c r="X21" s="70">
+        <v>0.20999999999999999</v>
+      </c>
+      <c r="Y21" s="70">
+        <v>0.20999999999999999</v>
+      </c>
+      <c r="Z21" s="135">
+        <v>0.39000000000000012</v>
+      </c>
+      <c r="AA21" s="103">
+        <v>0.18999999999999989</v>
+      </c>
+      <c r="AB21" s="136">
+        <v>0.35999999999999988</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="201"/>
-      <c r="B22" s="214" t="s">
-        <v>87</v>
+      <c r="A22" s="196"/>
+      <c r="B22" s="197" t="s">
+        <v>86</v>
       </c>
       <c r="C22" s="36" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D22" s="37" t="s">
-        <v>85</v>
-      </c>
-      <c r="E22" s="139">
-        <v>0.33000000000000013</v>
+        <v>83</v>
+      </c>
+      <c r="E22" s="94">
+        <v>2.5272995471999011</v>
       </c>
       <c r="F22" s="16">
-        <v>0.47999999999999998</v>
-      </c>
-      <c r="G22" s="69">
-        <v>0.31999999999999978</v>
-      </c>
-      <c r="H22" s="217">
-        <v>0.41000000000000009</v>
-      </c>
-      <c r="I22" s="109">
-        <v>0.37999999999999989</v>
-      </c>
-      <c r="J22" s="186">
-        <v>0.36999999999999972</v>
-      </c>
-      <c r="K22" s="128">
-        <v>0.29999999999999982</v>
-      </c>
-      <c r="L22" s="64">
-        <v>0.31000000000000011</v>
-      </c>
-      <c r="M22" s="218">
-        <v>0.35000000000000009</v>
-      </c>
-      <c r="N22" s="181">
-        <v>0.33999999999999991</v>
-      </c>
-      <c r="O22" s="69">
-        <v>0.31999999999999978</v>
-      </c>
-      <c r="P22" s="136">
-        <v>0.36000000000000032</v>
-      </c>
-      <c r="Q22" s="135">
-        <v>0.39000000000000012</v>
-      </c>
-      <c r="R22" s="64">
-        <v>0.30999999999999961</v>
-      </c>
-      <c r="S22" s="121">
-        <v>0.27000000000000002</v>
-      </c>
-      <c r="T22" s="179">
-        <v>0.41999999999999987</v>
-      </c>
-      <c r="U22" s="24">
-        <v>0.1699999999999999</v>
-      </c>
-      <c r="V22" s="139">
-        <v>0.33000000000000013</v>
-      </c>
-      <c r="W22" s="121">
-        <v>0.27000000000000002</v>
-      </c>
-      <c r="X22" s="70">
-        <v>0.20999999999999999</v>
-      </c>
-      <c r="Y22" s="70">
-        <v>0.20999999999999999</v>
-      </c>
-      <c r="Z22" s="135">
-        <v>0.39000000000000012</v>
-      </c>
-      <c r="AA22" s="103">
-        <v>0.18999999999999989</v>
-      </c>
-      <c r="AB22" s="136">
-        <v>0.35999999999999988</v>
+        <v>3.2165553482859992</v>
+      </c>
+      <c r="G22" s="214">
+        <v>2.2434356240379998</v>
+      </c>
+      <c r="H22" s="171">
+        <v>2.473722936558</v>
+      </c>
+      <c r="I22" s="169">
+        <v>2.4870291530649991</v>
+      </c>
+      <c r="J22" s="79">
+        <v>2.7567888748409999</v>
+      </c>
+      <c r="K22" s="192">
+        <v>1.6053585664479999</v>
+      </c>
+      <c r="L22" s="108">
+        <v>2.0140622432120008</v>
+      </c>
+      <c r="M22" s="199">
+        <v>2.369891690647</v>
+      </c>
+      <c r="N22" s="69">
+        <v>2.0123930879539991</v>
+      </c>
+      <c r="O22" s="24">
+        <v>0.88135507912899946</v>
+      </c>
+      <c r="P22" s="66">
+        <v>1.5279540404309999</v>
+      </c>
+      <c r="Q22" s="141">
+        <v>2.3334997801180002</v>
+      </c>
+      <c r="R22" s="22">
+        <v>2.0521843492570011</v>
+      </c>
+      <c r="S22" s="29">
+        <v>1.263532589456998</v>
+      </c>
+      <c r="T22" s="77">
+        <v>1.668210348613</v>
+      </c>
+      <c r="U22" s="83">
+        <v>1.374884702762001</v>
+      </c>
+      <c r="V22" s="210">
+        <v>1.4275701304010009</v>
+      </c>
+      <c r="W22" s="77">
+        <v>1.667726110617</v>
+      </c>
+      <c r="X22" s="203">
+        <v>1.299539839922</v>
+      </c>
+      <c r="Y22" s="215">
+        <v>1.019663280314999</v>
+      </c>
+      <c r="Z22" s="216">
+        <v>1.896910442517999</v>
+      </c>
+      <c r="AA22" s="157">
+        <v>1.095797337636</v>
+      </c>
+      <c r="AB22" s="141">
+        <v>2.3330034376</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="201"/>
-      <c r="B23" s="202" t="s">
+      <c r="A23" s="196"/>
+      <c r="B23" s="35"/>
+      <c r="C23" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="D23" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="C23" s="36" t="s">
-        <v>84</v>
-      </c>
-      <c r="D23" s="37" t="s">
-        <v>85</v>
-      </c>
-      <c r="E23" s="219">
-        <v>2.6000000000000001</v>
-      </c>
-      <c r="F23" s="16">
-        <v>3.1999999999999988</v>
-      </c>
-      <c r="G23" s="220">
-        <v>2.2000000000000011</v>
-      </c>
-      <c r="H23" s="135">
-        <v>2.5</v>
-      </c>
-      <c r="I23" s="221">
-        <v>2.3999999999999999</v>
-      </c>
-      <c r="J23" s="45">
-        <v>2.6999999999999988</v>
-      </c>
-      <c r="K23" s="28">
-        <v>1.6000000000000001</v>
-      </c>
-      <c r="L23" s="22">
-        <v>2</v>
-      </c>
-      <c r="M23" s="221">
-        <v>2.3999999999999999</v>
-      </c>
-      <c r="N23" s="22">
-        <v>2</v>
-      </c>
-      <c r="O23" s="24">
-        <v>0.79999999999999893</v>
-      </c>
-      <c r="P23" s="28">
-        <v>1.6000000000000001</v>
-      </c>
-      <c r="Q23" s="141">
-        <v>2.2999999999999989</v>
-      </c>
-      <c r="R23" s="203">
-        <v>2.1000000000000001</v>
-      </c>
-      <c r="S23" s="40">
-        <v>1.3000000000000009</v>
-      </c>
-      <c r="T23" s="28">
-        <v>1.6000000000000001</v>
-      </c>
-      <c r="U23" s="32">
-        <v>1.399999999999999</v>
-      </c>
-      <c r="V23" s="32">
-        <v>1.399999999999999</v>
-      </c>
-      <c r="W23" s="82">
-        <v>1.7000000000000011</v>
-      </c>
-      <c r="X23" s="40">
-        <v>1.3000000000000009</v>
-      </c>
-      <c r="Y23" s="95">
-        <v>1.100000000000001</v>
-      </c>
-      <c r="Z23" s="41">
-        <v>1.8999999999999999</v>
-      </c>
-      <c r="AA23" s="95">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="AB23" s="221">
-        <v>2.3999999999999999</v>
+      <c r="E23" s="16">
+        <v>3.427777777777778</v>
+      </c>
+      <c r="F23" s="15">
+        <v>2.8533333333333331</v>
+      </c>
+      <c r="G23" s="95">
+        <v>1.253333333333333</v>
+      </c>
+      <c r="H23" s="24">
+        <v>0.93444444444444485</v>
+      </c>
+      <c r="I23" s="120">
+        <v>1.0377777777777779</v>
+      </c>
+      <c r="J23" s="114">
+        <v>1.3944444444444439</v>
+      </c>
+      <c r="K23" s="217">
+        <v>2.3633333333333342</v>
+      </c>
+      <c r="L23" s="30">
+        <v>1.0033333333333341</v>
+      </c>
+      <c r="M23" s="134">
+        <v>2.0411111111111109</v>
+      </c>
+      <c r="N23" s="81">
+        <v>2.428888888888888</v>
+      </c>
+      <c r="O23" s="115">
+        <v>1.7944444444444441</v>
+      </c>
+      <c r="P23" s="213">
+        <v>2.3766666666666669</v>
+      </c>
+      <c r="Q23" s="41">
+        <v>2.0822222222222209</v>
+      </c>
+      <c r="R23" s="67">
+        <v>1.2866666666666671</v>
+      </c>
+      <c r="S23" s="26">
+        <v>1.416666666666667</v>
+      </c>
+      <c r="T23" s="186">
+        <v>3.123333333333334</v>
+      </c>
+      <c r="U23" s="83">
+        <v>1.461111111111111</v>
+      </c>
+      <c r="V23" s="85">
+        <v>1.8799999999999999</v>
+      </c>
+      <c r="W23" s="216">
+        <v>2.0155555555555549</v>
+      </c>
+      <c r="X23" s="87">
+        <v>1.125555555555555</v>
+      </c>
+      <c r="Y23" s="218">
+        <v>2.8944444444444439</v>
+      </c>
+      <c r="Z23" s="192">
+        <v>1.7044444444444451</v>
+      </c>
+      <c r="AA23" s="170">
+        <v>2.2177777777777781</v>
+      </c>
+      <c r="AB23" s="187">
+        <v>3.4122222222222218</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="201"/>
-      <c r="B24" s="210"/>
+      <c r="A24" s="196"/>
+      <c r="B24" s="205"/>
       <c r="C24" s="36" t="s">
         <v>89</v>
       </c>
       <c r="D24" s="37" t="s">
         <v>90</v>
       </c>
-      <c r="E24" s="16">
-        <v>3.427777777777778</v>
-      </c>
-      <c r="F24" s="15">
-        <v>2.8533333333333331</v>
-      </c>
-      <c r="G24" s="95">
-        <v>1.253333333333333</v>
-      </c>
-      <c r="H24" s="24">
-        <v>0.93444444444444485</v>
-      </c>
-      <c r="I24" s="120">
-        <v>1.0377777777777779</v>
-      </c>
-      <c r="J24" s="114">
-        <v>1.3944444444444439</v>
-      </c>
-      <c r="K24" s="222">
-        <v>2.3633333333333342</v>
-      </c>
-      <c r="L24" s="30">
-        <v>1.0033333333333341</v>
-      </c>
-      <c r="M24" s="134">
-        <v>2.0411111111111109</v>
-      </c>
-      <c r="N24" s="81">
-        <v>2.428888888888888</v>
-      </c>
-      <c r="O24" s="115">
-        <v>1.7944444444444441</v>
-      </c>
-      <c r="P24" s="218">
-        <v>2.3766666666666669</v>
-      </c>
-      <c r="Q24" s="41">
-        <v>2.0822222222222209</v>
-      </c>
-      <c r="R24" s="67">
-        <v>1.2866666666666671</v>
-      </c>
-      <c r="S24" s="26">
-        <v>1.416666666666667</v>
-      </c>
-      <c r="T24" s="182">
-        <v>3.123333333333334</v>
-      </c>
-      <c r="U24" s="83">
-        <v>1.461111111111111</v>
-      </c>
-      <c r="V24" s="85">
-        <v>1.8799999999999999</v>
-      </c>
-      <c r="W24" s="223">
-        <v>2.0155555555555549</v>
-      </c>
-      <c r="X24" s="87">
-        <v>1.125555555555555</v>
-      </c>
-      <c r="Y24" s="224">
-        <v>2.8944444444444439</v>
-      </c>
-      <c r="Z24" s="225">
-        <v>1.7044444444444451</v>
-      </c>
-      <c r="AA24" s="170">
-        <v>2.2177777777777781</v>
-      </c>
-      <c r="AB24" s="212">
-        <v>3.4122222222222218</v>
+      <c r="E24" s="219"/>
+      <c r="F24" s="219"/>
+      <c r="G24" s="219"/>
+      <c r="H24" s="219"/>
+      <c r="I24" s="52">
+        <v>3.109999999999999</v>
+      </c>
+      <c r="J24" s="134">
+        <v>3.8300000000000001</v>
+      </c>
+      <c r="K24" s="110">
+        <v>3.27</v>
+      </c>
+      <c r="L24" s="198">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="M24" s="149">
+        <v>5.4299999999999997</v>
+      </c>
+      <c r="N24" s="170">
+        <v>4.3299999999999992</v>
+      </c>
+      <c r="O24" s="139">
+        <v>4.3600000000000012</v>
+      </c>
+      <c r="P24" s="213">
+        <v>4.79</v>
+      </c>
+      <c r="Q24" s="16">
+        <v>7.7200000000000006</v>
+      </c>
+      <c r="R24" s="21">
+        <v>4.2000000000000002</v>
+      </c>
+      <c r="S24" s="29">
+        <v>1.8600000000000001</v>
+      </c>
+      <c r="T24" s="108">
+        <v>4.129999999999999</v>
+      </c>
+      <c r="U24" s="220">
+        <v>3.5600000000000001</v>
+      </c>
+      <c r="V24" s="72">
+        <v>3.48</v>
+      </c>
+      <c r="W24" s="132">
+        <v>4.4199999999999999</v>
+      </c>
+      <c r="X24" s="24">
+        <v>0.72999999999999954</v>
+      </c>
+      <c r="Y24" s="115">
+        <v>3.1499999999999999</v>
+      </c>
+      <c r="Z24" s="137">
+        <v>4.46</v>
+      </c>
+      <c r="AA24" s="61">
+        <v>2.4999999999999991</v>
+      </c>
+      <c r="AB24" s="126">
+        <v>3.79</v>
       </c>
     </row>
     <row r="25" ht="28.5">
-      <c r="A25" s="201"/>
-      <c r="B25" s="226" t="s">
+      <c r="A25" s="196"/>
+      <c r="B25" s="221" t="s">
         <v>91</v>
       </c>
       <c r="C25" s="36" t="s">
@@ -4746,19 +5139,19 @@
       <c r="D25" s="37" t="s">
         <v>93</v>
       </c>
-      <c r="E25" s="227">
+      <c r="E25" s="222">
         <v>97.390000000000001</v>
       </c>
-      <c r="F25" s="228">
+      <c r="F25" s="223">
         <v>95.410000000000011</v>
       </c>
-      <c r="G25" s="229">
+      <c r="G25" s="224">
         <v>91.740000000000009</v>
       </c>
-      <c r="H25" s="230">
+      <c r="H25" s="225">
         <v>96.260000000000005</v>
       </c>
-      <c r="I25" s="231">
+      <c r="I25" s="226">
         <v>92.290000000000006</v>
       </c>
       <c r="J25" s="16">
@@ -4767,7 +5160,7 @@
       <c r="K25" s="138">
         <v>82.340000000000003</v>
       </c>
-      <c r="L25" s="205">
+      <c r="L25" s="200">
         <v>89.010000000000005</v>
       </c>
       <c r="M25" s="125">
@@ -4782,7 +5175,7 @@
       <c r="P25" s="151">
         <v>88.310000000000002</v>
       </c>
-      <c r="Q25" s="232">
+      <c r="Q25" s="227">
         <v>89.650000000000006</v>
       </c>
       <c r="R25" s="24">
@@ -4791,31 +5184,31 @@
       <c r="S25" s="52">
         <v>54.759999999999991</v>
       </c>
-      <c r="T25" s="184">
+      <c r="T25" s="228">
         <v>91.109999999999999</v>
       </c>
-      <c r="U25" s="215">
+      <c r="U25" s="209">
         <v>68.609999999999999</v>
       </c>
       <c r="V25" s="102">
         <v>59.25</v>
       </c>
-      <c r="W25" s="233">
+      <c r="W25" s="229">
         <v>83.149999999999991</v>
       </c>
       <c r="X25" s="86">
         <v>69.789999999999992</v>
       </c>
-      <c r="Y25" s="234">
+      <c r="Y25" s="230">
         <v>67.480000000000004</v>
       </c>
-      <c r="Z25" s="235"/>
-      <c r="AA25" s="235"/>
-      <c r="AB25" s="235"/>
+      <c r="Z25" s="219"/>
+      <c r="AA25" s="219"/>
+      <c r="AB25" s="219"/>
     </row>
     <row r="26" ht="28.5">
-      <c r="A26" s="201"/>
-      <c r="B26" s="226" t="s">
+      <c r="A26" s="196"/>
+      <c r="B26" s="221" t="s">
         <v>94</v>
       </c>
       <c r="C26" s="36" t="s">
@@ -4827,19 +5220,19 @@
       <c r="E26" s="171">
         <v>72.732200000000006</v>
       </c>
-      <c r="F26" s="236">
+      <c r="F26" s="231">
         <v>83.296330000000012</v>
       </c>
-      <c r="G26" s="237">
+      <c r="G26" s="232">
         <v>80.017300000000006</v>
       </c>
       <c r="H26" s="127">
         <v>77.129459999999995</v>
       </c>
-      <c r="I26" s="182">
+      <c r="I26" s="186">
         <v>80.170400000000001</v>
       </c>
-      <c r="J26" s="238">
+      <c r="J26" s="233">
         <v>79.309809999999999</v>
       </c>
       <c r="K26" s="16">
@@ -4857,7 +5250,7 @@
       <c r="O26" s="135">
         <v>73.829080000000005</v>
       </c>
-      <c r="P26" s="227">
+      <c r="P26" s="222">
         <v>83.376289999999997</v>
       </c>
       <c r="Q26" s="62">
@@ -4872,7 +5265,7 @@
       <c r="T26" s="48">
         <v>63.313799999999993</v>
       </c>
-      <c r="U26" s="239">
+      <c r="U26" s="190">
         <v>74.11099999999999</v>
       </c>
       <c r="V26" s="85">
@@ -4887,17 +5280,17 @@
       <c r="Y26" s="151">
         <v>78.379899999999992</v>
       </c>
-      <c r="Z26" s="235"/>
-      <c r="AA26" s="235"/>
-      <c r="AB26" s="235"/>
+      <c r="Z26" s="219"/>
+      <c r="AA26" s="219"/>
+      <c r="AB26" s="219"/>
     </row>
     <row r="27">
-      <c r="A27" s="201"/>
-      <c r="B27" s="214" t="s">
+      <c r="A27" s="196"/>
+      <c r="B27" s="208" t="s">
         <v>97</v>
       </c>
       <c r="C27" s="36" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D27" s="37" t="s">
         <v>98</v>
@@ -4905,19 +5298,19 @@
       <c r="E27" s="113">
         <v>48.869999999999997</v>
       </c>
-      <c r="F27" s="240">
+      <c r="F27" s="234">
         <v>84.419999999999987</v>
       </c>
       <c r="G27" s="24">
         <v>41.079999999999998</v>
       </c>
-      <c r="H27" s="213">
+      <c r="H27" s="207">
         <v>48.340000000000003</v>
       </c>
       <c r="I27" s="41">
         <v>62.209999999999987</v>
       </c>
-      <c r="J27" s="241">
+      <c r="J27" s="235">
         <v>77.850000000000009</v>
       </c>
       <c r="K27" s="135">
@@ -4932,10 +5325,10 @@
       <c r="N27" s="73">
         <v>84.640000000000001</v>
       </c>
-      <c r="O27" s="242">
+      <c r="O27" s="236">
         <v>63.18</v>
       </c>
-      <c r="P27" s="212">
+      <c r="P27" s="187">
         <v>86.950000000000003</v>
       </c>
       <c r="Q27" s="47">
@@ -4956,7 +5349,7 @@
       <c r="V27" s="135">
         <v>73.829999999999998</v>
       </c>
-      <c r="W27" s="243">
+      <c r="W27" s="237">
         <v>73.189999999999998</v>
       </c>
       <c r="X27" s="175">
@@ -4976,8 +5369,8 @@
       </c>
     </row>
     <row r="28" ht="28.5">
-      <c r="A28" s="201"/>
-      <c r="B28" s="226" t="s">
+      <c r="A28" s="196"/>
+      <c r="B28" s="221" t="s">
         <v>99</v>
       </c>
       <c r="C28" s="36" t="s">
@@ -4986,7 +5379,7 @@
       <c r="D28" s="37" t="s">
         <v>101</v>
       </c>
-      <c r="E28" s="235"/>
+      <c r="E28" s="219"/>
       <c r="F28" s="16">
         <v>57.750000000000007</v>
       </c>
@@ -4996,7 +5389,7 @@
       <c r="H28" s="112">
         <v>41.819999999999993</v>
       </c>
-      <c r="I28" s="244">
+      <c r="I28" s="238">
         <v>43.68</v>
       </c>
       <c r="J28" s="47">
@@ -5008,7 +5401,7 @@
       <c r="L28" s="55">
         <v>19.09</v>
       </c>
-      <c r="M28" s="187">
+      <c r="M28" s="239">
         <v>31.699999999999999</v>
       </c>
       <c r="N28" s="175">
@@ -5017,7 +5410,7 @@
       <c r="O28" s="81">
         <v>41.029999999999987</v>
       </c>
-      <c r="P28" s="245">
+      <c r="P28" s="240">
         <v>39.369999999999997</v>
       </c>
       <c r="Q28" s="52">
@@ -5032,7 +5425,7 @@
       <c r="T28" s="113">
         <v>23.25</v>
       </c>
-      <c r="U28" s="196">
+      <c r="U28" s="241">
         <v>25.489999999999998</v>
       </c>
       <c r="V28" s="147">
@@ -5044,7 +5437,7 @@
       <c r="X28" s="158">
         <v>20.719999999999999</v>
       </c>
-      <c r="Y28" s="246">
+      <c r="Y28" s="242">
         <v>24.059999999999999</v>
       </c>
       <c r="Z28" s="24">
@@ -5058,8 +5451,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="201"/>
-      <c r="B29" s="214" t="s">
+      <c r="A29" s="196"/>
+      <c r="B29" s="208" t="s">
         <v>102</v>
       </c>
       <c r="C29" s="36" t="s">
@@ -5077,7 +5470,7 @@
       <c r="G29" s="133">
         <v>0.41999999999999998</v>
       </c>
-      <c r="H29" s="247">
+      <c r="H29" s="243">
         <v>0.47999999999999998</v>
       </c>
       <c r="I29" s="110">
@@ -5086,7 +5479,7 @@
       <c r="J29" s="16">
         <v>2</v>
       </c>
-      <c r="K29" s="248">
+      <c r="K29" s="244">
         <v>0.46000000000000002</v>
       </c>
       <c r="L29" s="167">
@@ -5095,7 +5488,7 @@
       <c r="M29" s="114">
         <v>0.69000000000000006</v>
       </c>
-      <c r="N29" s="249">
+      <c r="N29" s="245">
         <v>0.95000000000000007</v>
       </c>
       <c r="O29" s="78">
@@ -5110,28 +5503,28 @@
       <c r="R29" s="24">
         <v>0.39000000000000001</v>
       </c>
-      <c r="S29" s="247">
+      <c r="S29" s="243">
         <v>0.47999999999999998</v>
       </c>
       <c r="T29" s="171">
         <v>1.49</v>
       </c>
-      <c r="U29" s="209">
+      <c r="U29" s="204">
         <v>0.45000000000000001</v>
       </c>
-      <c r="V29" s="209">
+      <c r="V29" s="204">
         <v>0.45000000000000012</v>
       </c>
       <c r="W29" s="119">
         <v>0.66999999999999993</v>
       </c>
-      <c r="X29" s="213">
+      <c r="X29" s="207">
         <v>0.64000000000000012</v>
       </c>
       <c r="Y29" s="70">
         <v>0.60000000000000009</v>
       </c>
-      <c r="Z29" s="196">
+      <c r="Z29" s="241">
         <v>0.75</v>
       </c>
       <c r="AA29" s="51">
@@ -5142,8 +5535,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="201"/>
-      <c r="B30" s="214" t="s">
+      <c r="A30" s="196"/>
+      <c r="B30" s="208" t="s">
         <v>105</v>
       </c>
       <c r="C30" s="36" t="s">
@@ -5152,20 +5545,20 @@
       <c r="D30" s="37" t="s">
         <v>107</v>
       </c>
-      <c r="E30" s="235"/>
+      <c r="E30" s="219"/>
       <c r="F30" s="123">
         <v>41.299999999999997</v>
       </c>
       <c r="G30" s="174">
         <v>37.600000000000001</v>
       </c>
-      <c r="H30" s="245">
+      <c r="H30" s="240">
         <v>29.600000000000001</v>
       </c>
       <c r="I30" s="127">
         <v>39.799999999999997</v>
       </c>
-      <c r="J30" s="250">
+      <c r="J30" s="246">
         <v>43.700000000000003</v>
       </c>
       <c r="K30" s="112">
@@ -5177,16 +5570,16 @@
       <c r="M30" s="151">
         <v>41</v>
       </c>
-      <c r="N30" s="217">
+      <c r="N30" s="211">
         <v>38.799999999999997</v>
       </c>
-      <c r="O30" s="221">
+      <c r="O30" s="247">
         <v>34.200000000000003</v>
       </c>
-      <c r="P30" s="251">
+      <c r="P30" s="248">
         <v>44</v>
       </c>
-      <c r="Q30" s="252">
+      <c r="Q30" s="249">
         <v>40.899999999999999</v>
       </c>
       <c r="R30" s="152">
@@ -5195,7 +5588,7 @@
       <c r="S30" s="97">
         <v>24</v>
       </c>
-      <c r="T30" s="253">
+      <c r="T30" s="184">
         <v>43.299999999999997</v>
       </c>
       <c r="U30" s="24">
@@ -5207,7 +5600,7 @@
       <c r="W30" s="16">
         <v>48.200000000000003</v>
       </c>
-      <c r="X30" s="206">
+      <c r="X30" s="201">
         <v>17.199999999999999</v>
       </c>
       <c r="Y30" s="148">
@@ -5216,99 +5609,99 @@
       <c r="Z30" s="140">
         <v>16</v>
       </c>
-      <c r="AA30" s="254">
+      <c r="AA30" s="250">
         <v>36.099999999999987</v>
       </c>
-      <c r="AB30" s="244">
+      <c r="AB30" s="238">
         <v>34</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="255"/>
-      <c r="B31" s="256" t="s">
+      <c r="A31" s="251"/>
+      <c r="B31" s="252" t="s">
         <v>108</v>
       </c>
       <c r="C31" s="91" t="s">
         <v>95</v>
       </c>
       <c r="D31" s="92" t="s">
-        <v>83</v>
-      </c>
-      <c r="E31" s="257">
-        <v>5.8192583240551201</v>
-      </c>
-      <c r="F31" s="175">
-        <v>6.6425682843577274</v>
-      </c>
-      <c r="G31" s="23">
-        <v>5.4540993681073786</v>
-      </c>
-      <c r="H31" s="242">
-        <v>5.3526061699153864</v>
-      </c>
-      <c r="I31" s="222">
-        <v>5.6720952183864313</v>
-      </c>
-      <c r="J31" s="182">
-        <v>6.6974456856480131</v>
-      </c>
-      <c r="K31" s="186">
-        <v>5.9220809743072111</v>
+        <v>81</v>
+      </c>
+      <c r="E31" s="144">
+        <v>5.8177279193468561</v>
+      </c>
+      <c r="F31" s="162">
+        <v>6.6123458647944711</v>
+      </c>
+      <c r="G31" s="47">
+        <v>5.4775810424809883</v>
+      </c>
+      <c r="H31" s="165">
+        <v>5.3755337117943487</v>
+      </c>
+      <c r="I31" s="86">
+        <v>5.6740799153754562</v>
+      </c>
+      <c r="J31" s="175">
+        <v>6.6967789107237738</v>
+      </c>
+      <c r="K31" s="253">
+        <v>5.899060000845691</v>
       </c>
       <c r="L31" s="24">
-        <v>3.7310897061155841</v>
+        <v>3.7340696389918429</v>
       </c>
       <c r="M31" s="16">
-        <v>7.1205598525011666</v>
-      </c>
-      <c r="N31" s="231">
-        <v>6.7392051262721004</v>
-      </c>
-      <c r="O31" s="237">
-        <v>6.6926350104367964</v>
-      </c>
-      <c r="P31" s="230">
-        <v>6.9377300834483604</v>
-      </c>
-      <c r="Q31" s="239">
-        <v>6.1541501293850773</v>
-      </c>
-      <c r="R31" s="258">
-        <v>4.6118147287067597</v>
-      </c>
-      <c r="S31" s="135">
-        <v>6.128081452416362</v>
-      </c>
-      <c r="T31" s="240">
-        <v>6.9137373506596838</v>
-      </c>
-      <c r="U31" s="259">
-        <v>5.9610053396232736</v>
-      </c>
-      <c r="V31" s="250">
-        <v>6.7565447172132354</v>
-      </c>
-      <c r="W31" s="172">
-        <v>7.022799524840285</v>
-      </c>
-      <c r="X31" s="21">
-        <v>5.4184679676784988</v>
-      </c>
-      <c r="Y31" s="260">
-        <v>5.3153149429166078</v>
-      </c>
-      <c r="Z31" s="235"/>
-      <c r="AA31" s="235"/>
-      <c r="AB31" s="235"/>
+        <v>7.1907062458691744</v>
+      </c>
+      <c r="N31" s="184">
+        <v>6.7946753835196922</v>
+      </c>
+      <c r="O31" s="228">
+        <v>6.7326778322541596</v>
+      </c>
+      <c r="P31" s="11">
+        <v>6.8789314325175068</v>
+      </c>
+      <c r="Q31" s="94">
+        <v>6.1667068644882166</v>
+      </c>
+      <c r="R31" s="201">
+        <v>4.6395278013315631</v>
+      </c>
+      <c r="S31" s="254">
+        <v>6.1480404672655196</v>
+      </c>
+      <c r="T31" s="39">
+        <v>6.9264452812872888</v>
+      </c>
+      <c r="U31" s="176">
+        <v>5.9922720096597448</v>
+      </c>
+      <c r="V31" s="184">
+        <v>6.7936017073548669</v>
+      </c>
+      <c r="W31" s="222">
+        <v>7.058032619227653</v>
+      </c>
+      <c r="X31" s="236">
+        <v>5.3867863766576214</v>
+      </c>
+      <c r="Y31" s="41">
+        <v>5.3204951029172243</v>
+      </c>
+      <c r="Z31" s="219"/>
+      <c r="AA31" s="219"/>
+      <c r="AB31" s="219"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A3:A17"/>
+    <mergeCell ref="A3:A16"/>
     <mergeCell ref="B3:B7"/>
-    <mergeCell ref="B8:B16"/>
-    <mergeCell ref="A18:A31"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="B8:B15"/>
+    <mergeCell ref="A17:A31"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="B22:B24"/>
   </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
